--- a/diseases/d026/2020-2025.xlsx
+++ b/diseases/d026/2020-2025.xlsx
@@ -1075,9 +1075,6 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.2727664519085469</v>
       </c>
@@ -5185,9 +5182,6 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.2683529968991811</v>
       </c>
@@ -27809,9 +27803,6 @@
       <c r="O183" t="n">
         <v>41</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.4595391987496947</v>
       </c>
@@ -37676,9 +37667,6 @@
       </c>
       <c r="O249" t="n">
         <v>24</v>
-      </c>
-      <c r="Q249" t="n">
-        <v>0</v>
       </c>
       <c r="R249" t="n">
         <v>0.2676358802697435</v>

--- a/diseases/d026/2020-2025.xlsx
+++ b/diseases/d026/2020-2025.xlsx
@@ -938,28 +938,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1627,28 +1641,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2071,28 +2099,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2515,28 +2557,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -2959,28 +3015,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3107,28 +3177,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3255,28 +3339,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -3551,28 +3649,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -3699,28 +3811,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -3995,28 +4121,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4439,28 +4579,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -4587,28 +4741,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5045,28 +5213,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -5586,28 +5768,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -5734,28 +5930,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -6030,28 +6240,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -6178,28 +6402,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -6326,28 +6564,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -6622,28 +6874,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6770,28 +7036,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -7214,28 +7494,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -7510,28 +7804,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7954,28 +8262,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -8398,28 +8720,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8856,28 +9192,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -9596,28 +9946,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -10336,28 +10700,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -11076,28 +11454,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -11964,28 +12356,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -12704,28 +13110,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -13444,28 +13864,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -14332,28 +14766,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -15072,28 +15520,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -15812,28 +16274,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -16700,28 +17176,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -17440,28 +17930,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -18490,28 +18994,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -19230,28 +19748,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -19970,28 +20502,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -20562,28 +21108,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -21450,28 +22010,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -22190,28 +22764,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -22930,28 +23518,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -23818,28 +24420,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -24558,28 +25174,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -25446,28 +26076,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -26186,28 +26830,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -26926,28 +27584,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -28207,28 +28879,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
@@ -28947,28 +29633,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -29687,28 +30387,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -30575,28 +31289,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -31315,28 +32043,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
@@ -32055,28 +32797,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -32943,28 +33699,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
@@ -33683,28 +34453,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
@@ -34571,28 +35355,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
@@ -35311,28 +36109,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
@@ -36051,28 +36863,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
@@ -36939,28 +37765,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
@@ -38072,28 +38912,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
@@ -38220,28 +39074,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
@@ -38368,28 +39236,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
@@ -38516,28 +39398,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
@@ -38664,28 +39560,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
@@ -38812,28 +39722,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
@@ -38960,28 +39884,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
@@ -39108,28 +40046,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
@@ -39256,28 +40208,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
@@ -39404,28 +40370,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
@@ -39552,28 +40532,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
@@ -39700,28 +40694,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_CN_TYPHOID_PARATYPHOID_COMBINED_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
